--- a/tender-system/reports/ISP-обзвон-ИТОГ-2026-08-26.xlsx
+++ b/tender-system/reports/ISP-обзвон-ИТОГ-2026-08-26.xlsx
@@ -7,14 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P1 · ОТДЕЛКА (краска+гипсокартон+полы)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P2 · УБОРКА (final clean)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="P3 · ДЕМОНТАЖ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="P1 · Отделка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P2 · Уборка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="P3 · Демонтаж" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'P1 · ОТДЕЛКА (краска+гипсокартон+полы)'!$A$2:$L$512</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P2 · УБОРКА (final clean)'!$A$2:$L$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'P3 · ДЕМОНТАЖ'!$A$2:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'P1 · Отделка'!$A$2:$L$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P2 · Уборка'!$A$2:$L$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'P3 · Демонтаж'!$A$2:$L$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -538,7 +538,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P1 · ОТДЕЛКА (краска+гипсокартон+полы) · 510 объектов · Miami-Dade · активные (CO нет) · свежесть ≤180д · звони по «Телефон GC»; ✓ = номер подтверждён вебом</t>
+          <t>P1 · Отделка — Покраска + гипсокартон + полы · 510 объектов · Miami-Dade · активные (CO нет) · свежесть ≤180д · звони по «Телефон GC»; ✓ = номер подтверждён вебом</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>P2 · УБОРКА (final clean) · 110 объектов · Miami-Dade · активные (CO нет) · свежесть ≤180д · звони по «Телефон GC»; ✓ = номер подтверждён вебом</t>
+          <t>P2 · Уборка — Final clean после стройки · 110 объектов · Miami-Dade · активные (CO нет) · свежесть ≤180д · звони по «Телефон GC»; ✓ = номер подтверждён вебом</t>
         </is>
       </c>
     </row>
@@ -34800,7 +34800,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>P3 · ДЕМОНТАЖ · 63 объектов · Miami-Dade · активные (CO нет) · свежесть ≤180д · звони по «Телефон GC»; ✓ = номер подтверждён вебом</t>
+          <t>P3 · Демонтаж — Демонтаж / вывоз мусора · 63 объектов · Miami-Dade · активные (CO нет) · свежесть ≤180д · звони по «Телефон GC»; ✓ = номер подтверждён вебом</t>
         </is>
       </c>
     </row>
